--- a/data/trans_dic/IP41-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP41-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que está casado y/o que vive en pareja</t>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>79,31; 93,82</t>
+          <t>78,68; 93,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,87; 97,01</t>
+          <t>85,53; 97,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,85; 93,3</t>
+          <t>79,59; 93,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,96; 91,88</t>
+          <t>76,41; 91,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,18; 96,12</t>
+          <t>83,17; 95,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,37; 91,66</t>
+          <t>76,03; 91,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79,97; 90,95</t>
+          <t>80,45; 90,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87,55; 95,43</t>
+          <t>87,47; 95,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79,52; 90,75</t>
+          <t>80,13; 90,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>85,1; 94,58</t>
+          <t>84,85; 94,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,47; 95,1</t>
+          <t>85,45; 94,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80,34; 90,9</t>
+          <t>80,18; 91,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,25; 95,8</t>
+          <t>87,5; 96,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,33; 91,83</t>
+          <t>81,99; 91,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,72; 83,67</t>
+          <t>70,82; 84,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87,61; 94,29</t>
+          <t>87,74; 94,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85,22; 92,02</t>
+          <t>85,34; 92,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76,77; 85,7</t>
+          <t>77,37; 85,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,67; 97,83</t>
+          <t>88,14; 97,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,29; 95,5</t>
+          <t>82,94; 95,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71,41; 88,95</t>
+          <t>72,04; 89,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>87,83; 97,3</t>
+          <t>87,44; 97,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84,7; 95,28</t>
+          <t>84,52; 96,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,5; 89,99</t>
+          <t>75,17; 90,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90,41; 96,59</t>
+          <t>90,06; 96,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>86,43; 94,32</t>
+          <t>86,39; 94,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75,96; 87,73</t>
+          <t>76,33; 87,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85,6; 96,14</t>
+          <t>84,82; 95,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80,28; 93,32</t>
+          <t>80,94; 93,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,5; 93,64</t>
+          <t>79,84; 93,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,66; 96,75</t>
+          <t>88,6; 96,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,17; 93,51</t>
+          <t>81,68; 93,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,42; 93,25</t>
+          <t>81,32; 93,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88,53; 95,8</t>
+          <t>88,12; 95,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83,66; 92,48</t>
+          <t>83,41; 92,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83,34; 92,03</t>
+          <t>83,45; 92,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>76,85; 93,79</t>
+          <t>77,4; 93,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>81,09; 96,94</t>
+          <t>82,05; 96,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,42; 98,49</t>
+          <t>86,19; 98,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>87,32; 98,47</t>
+          <t>87,09; 98,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,9; 91,81</t>
+          <t>73,38; 92,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,69; 91,11</t>
+          <t>73,03; 91,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>84,96; 95,34</t>
+          <t>85,63; 95,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81,31; 92,78</t>
+          <t>81,2; 93,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82,02; 93,27</t>
+          <t>81,57; 93,49</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>77,61; 93,85</t>
+          <t>79,35; 92,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>86,05; 97,82</t>
+          <t>85,93; 97,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73,23; 90,66</t>
+          <t>72,94; 90,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>86,65; 97,06</t>
+          <t>86,61; 96,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79,94; 93,77</t>
+          <t>80,73; 94,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>78,25; 93,52</t>
+          <t>79,25; 94,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>85,29; 94,32</t>
+          <t>85,13; 93,9</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>85,78; 94,84</t>
+          <t>86,35; 95,02</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>79,39; 90,87</t>
+          <t>79,19; 90,91</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,79; 96,12</t>
+          <t>88,33; 96,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>81,76; 91,08</t>
+          <t>81,38; 91,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65,8; 78,04</t>
+          <t>65,07; 77,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,22; 95,58</t>
+          <t>88,17; 96,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,47; 93,33</t>
+          <t>84,83; 93,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,81; 83,87</t>
+          <t>72,61; 84,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>89,24; 94,96</t>
+          <t>89,79; 95,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85,02; 91,24</t>
+          <t>85,07; 91,41</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70,83; 79,55</t>
+          <t>71,15; 79,35</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,54</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>87,7; 94,69</t>
+          <t>86,92; 94,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>80,9; 90,07</t>
+          <t>81,44; 89,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83,98; 91,72</t>
+          <t>83,89; 92,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>88,5; 95,42</t>
+          <t>89,34; 95,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,91; 89,66</t>
+          <t>81,08; 89,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,35; 92,03</t>
+          <t>83,89; 91,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>89,15; 94,25</t>
+          <t>89,46; 94,34</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>82,91; 89,21</t>
+          <t>82,98; 89,01</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85,46; 91,06</t>
+          <t>85,6; 91,14</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>89,21; 92,68</t>
+          <t>89,09; 92,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87,23; 91,04</t>
+          <t>87,17; 90,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>81,72; 86,33</t>
+          <t>81,58; 86,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>90,57; 93,92</t>
+          <t>90,68; 93,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>86,16; 90,13</t>
+          <t>86,18; 90,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>81,43; 85,92</t>
+          <t>81,4; 85,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>90,55; 92,95</t>
+          <t>90,53; 92,91</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>87,33; 89,99</t>
+          <t>87,36; 90,05</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>82,22; 85,45</t>
+          <t>82,43; 85,44</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>45577</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52742</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>50113</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>50434</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>58962</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>54761</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>96011</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>111704</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>104874</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>40822; 48554</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>48503; 55024</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>45659; 53674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>44975; 54091</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>53904; 61702</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>49011; 59098</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>89089; 100679</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>106294; 115818</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>97626; 110492</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>89471</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>95586</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>89101</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99234</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97112</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>84568</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>188705</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>192697</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>173669</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>83763; 93561</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89476; 99429</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>82622; 93936</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>94028; 103520</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>91134; 101971</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>77196; 91671</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>180910; 194246</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>184228; 199383</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>164049; 181945</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>63870</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>61653</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>54353</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>65329</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>65161</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>58399</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>129199</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>126814</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>112752</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>59578; 66136</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56548; 65237</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>48143; 59627</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>60959; 67834</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>60226; 68535</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>52544; 62967</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>123658; 132806</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>120461; 131841</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>104372; 119846</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>67435</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>68477</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>67765</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>73884</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>73026</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>71503</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>141319</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>141503</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>139268</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>62243; 70379</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>62940; 72572</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>61445; 71756</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>70089; 76728</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>67166; 77239</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>66019; 76026</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>134372; 145537</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>133448; 147533</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>131966; 145915</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>35216</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>40241</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>40836</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>42013</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>39582</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38864</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>77229</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>79824</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>79700</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>31298; 37909</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>36020; 42550</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>37439; 42704</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>38419; 43445</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>34306; 43016</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>33849; 42274</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>72406; 80707</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>73611; 84342</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>73238; 83947</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>49274</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>52510</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>45335</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>54920</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>53470</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>50667</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>104194</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>105980</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>96002</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>44477; 52076</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>48110; 54766</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>39588; 49326</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>51204; 57313</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>48637; 56963</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>45756; 54351</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>98044; 108153</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>100360; 110436</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>88705; 101835</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>118655</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>120667</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>99098</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>124240</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>130870</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>113306</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>242895</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>251537</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>212404</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>113006; 122889</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>112889; 126465</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>89395; 106134</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>118402; 128907</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>123625; 135826</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>104611; 121155</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>235459; 249319</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>241978; 260020</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>200251; 223316</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>141976</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>141847</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>145674</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>151084</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>147049</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>150703</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>293060</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>288896</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>296378</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>134949; 146777</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>134138; 148089</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>137730; 151784</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>145603; 155753</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>138910; 153713</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>143327; 156895</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>284679; 300218</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>278838; 299088</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>286793; 305328</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>611473</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>633723</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>592276</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>661138</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>665232</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>622770</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1272611</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>1298955</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>1215045</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>598015; 623118</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>619496; 646671</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>573893; 606252</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>648912; 671860</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>649341; 679132</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>605264; 638164</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1255626; 1288520</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>1279167; 1318438</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>1192798; 1236343</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP41-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP41-Provincia-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -519,15 +519,12 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,23 +535,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -576,47 +570,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -632,9 +611,6 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -664,47 +640,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>91,92%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
           <t>86,08%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -717,62 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,68; 93,58</t>
+          <t>78,47; 93,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,53; 97,03</t>
+          <t>85,3; 97,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,59; 93,56</t>
+          <t>79,11; 93,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>77,22; 91,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,41; 91,9</t>
+          <t>83,73; 95,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,17; 95,21</t>
+          <t>74,66; 91,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,03; 91,68</t>
+          <t>80,85; 91,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,3; 95,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>80,45; 90,91</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>87,47; 95,31</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>80,13; 90,69</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>79,59; 90,46</t>
         </is>
       </c>
     </row>
@@ -804,47 +750,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89,26%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
           <t>81,9%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -857,62 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,85; 94,78</t>
+          <t>84,77; 94,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,45; 94,95</t>
+          <t>85,09; 95,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80,18; 91,16</t>
+          <t>80,57; 91,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,66; 95,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,5; 96,33</t>
+          <t>82,08; 92,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,99; 91,73</t>
+          <t>71,26; 84,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,82; 84,1</t>
+          <t>88,26; 94,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,26; 92,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87,74; 94,21</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>85,34; 92,36</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>77,37; 85,81</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>77,21; 85,79</t>
         </is>
       </c>
     </row>
@@ -944,47 +860,32 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>90,95%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
           <t>82,46%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -997,62 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88,14; 97,84</t>
+          <t>88,29; 97,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,94; 95,69</t>
+          <t>83,6; 95,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72,04; 89,22</t>
+          <t>71,04; 88,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,41; 97,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>87,44; 97,31</t>
+          <t>85,59; 96,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84,52; 96,18</t>
+          <t>75,34; 90,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,17; 90,07</t>
+          <t>89,49; 96,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,27; 94,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90,06; 96,72</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>86,39; 94,56</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>76,33; 87,65</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>76,12; 87,93</t>
         </is>
       </c>
     </row>
@@ -1084,47 +970,32 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>88,44%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
           <t>88,06%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,82; 95,91</t>
+          <t>85,33; 96,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80,94; 93,33</t>
+          <t>80,94; 93,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,84; 93,24</t>
+          <t>80,76; 93,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,73; 96,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,6; 96,99</t>
+          <t>80,55; 93,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,68; 93,93</t>
+          <t>80,04; 93,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,32; 93,65</t>
+          <t>88,86; 95,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>83,32; 92,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88,12; 95,44</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>83,41; 92,21</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>83,45; 92,27</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>83,61; 92,18</t>
         </is>
       </c>
     </row>
@@ -1224,47 +1080,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>88,05%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
           <t>88,76%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>77,4; 93,75</t>
+          <t>75,46; 93,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,05; 96,92</t>
+          <t>82,7; 96,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,19; 98,31</t>
+          <t>86,27; 98,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,14; 98,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>87,09; 98,48</t>
+          <t>74,82; 92,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,38; 92,01</t>
+          <t>72,99; 91,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,03; 91,21</t>
+          <t>85,66; 95,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>81,78; 93,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>85,63; 95,45</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>81,2; 93,04</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>81,57; 93,49</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>82,46; 93,52</t>
         </is>
       </c>
     </row>
@@ -1364,47 +1190,32 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>91,18%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
           <t>85,71%</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>79,35; 92,9</t>
+          <t>79,49; 92,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85,93; 97,82</t>
+          <t>87,06; 97,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72,94; 90,88</t>
+          <t>74,52; 90,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,82; 96,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>86,61; 96,94</t>
+          <t>79,68; 93,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>80,73; 94,55</t>
+          <t>77,87; 94,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,25; 94,13</t>
+          <t>85,38; 94,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,8; 94,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>85,13; 93,9</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>86,35; 95,02</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>79,19; 90,91</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>78,95; 90,51</t>
         </is>
       </c>
     </row>
@@ -1504,47 +1300,32 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>88,43%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
           <t>75,47%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,33; 96,06</t>
+          <t>88,31; 96,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>81,38; 91,17</t>
+          <t>81,59; 91,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65,07; 77,26</t>
+          <t>65,39; 78,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>88,66; 95,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,17; 96,0</t>
+          <t>84,68; 93,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,83; 93,2</t>
+          <t>72,3; 83,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,61; 84,09</t>
+          <t>89,71; 94,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>84,98; 91,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>89,79; 95,08</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>85,07; 91,41</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>71,15; 79,35</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>71,4; 79,61</t>
         </is>
       </c>
     </row>
@@ -1644,47 +1410,32 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>85,98%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
           <t>88,46%</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>86,92; 94,54</t>
+          <t>87,09; 94,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>81,44; 89,91</t>
+          <t>81,4; 90,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83,89; 92,45</t>
+          <t>84,76; 92,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>88,78; 95,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>89,34; 95,57</t>
+          <t>81,34; 89,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>81,08; 89,73</t>
+          <t>83,65; 91,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,89; 91,83</t>
+          <t>88,96; 94,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>82,25; 88,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>89,46; 94,34</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>82,98; 89,01</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>85,6; 91,14</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>85,68; 91,28</t>
         </is>
       </c>
     </row>
@@ -1784,47 +1520,32 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>88,72%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
           <t>83,97%</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>89,09; 92,83</t>
+          <t>89,0; 92,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87,17; 90,99</t>
+          <t>87,29; 91,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>81,58; 86,18</t>
+          <t>81,96; 86,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,69; 93,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>90,68; 93,88</t>
+          <t>86,2; 90,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>86,18; 90,13</t>
+          <t>81,32; 85,84</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>81,4; 85,83</t>
+          <t>90,55; 92,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,25; 90,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>90,53; 92,91</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>87,36; 90,05</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>82,43; 85,44</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>82,42; 85,46</t>
         </is>
       </c>
     </row>
@@ -1905,17 +1611,17 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A14:A15"/>
   </mergeCells>
@@ -1929,7 +1635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1943,15 +1649,12 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1962,23 +1665,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2000,47 +1700,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -2056,9 +1741,6 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2088,47 +1770,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>145</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>161</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
           <t>160</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2156,47 +1823,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50434</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50434</t>
+          <t>58962</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58962</t>
+          <t>54761</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54761</t>
+          <t>96011</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>111704</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>96011</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>111704</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
           <t>104874</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2209,62 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40822; 48554</t>
+          <t>40712; 48676</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48503; 55024</t>
+          <t>48373; 55193</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45659; 53674</t>
+          <t>45384; 53407</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45450; 54075</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>44975; 54091</t>
+          <t>54265; 61787</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53904; 61702</t>
+          <t>48128; 58721</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49011; 59098</t>
+          <t>89534; 101105</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>106088; 115743</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>89089; 100679</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>106294; 115818</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>97626; 110492</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>96970; 110208</t>
         </is>
       </c>
     </row>
@@ -2296,47 +1933,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>289</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>283</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
           <t>258</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2364,47 +1986,32 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99234</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99234</t>
+          <t>97112</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97112</t>
+          <t>84568</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84568</t>
+          <t>188705</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>192697</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>188705</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>192697</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
           <t>173669</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83763; 93561</t>
+          <t>83686; 93507</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89476; 99429</t>
+          <t>89095; 99519</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82622; 93936</t>
+          <t>83021; 93829</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>94205; 103156</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>94028; 103520</t>
+          <t>91238; 102278</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91134; 101971</t>
+          <t>77667; 92174</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77196; 91671</t>
+          <t>181966; 194621</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>184050; 199009</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>180910; 194246</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>184228; 199383</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>164049; 181945</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>163712; 181906</t>
         </is>
       </c>
     </row>
@@ -2504,47 +2096,32 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>193</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>178</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
           <t>156</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2572,47 +2149,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65329</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65329</t>
+          <t>65161</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65161</t>
+          <t>58399</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58399</t>
+          <t>129199</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>126814</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>129199</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>126814</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
           <t>112752</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>59578; 66136</t>
+          <t>59684; 66134</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56548; 65237</t>
+          <t>56997; 65114</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48143; 59627</t>
+          <t>47477; 59160</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>60938; 67826</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>60959; 67834</t>
+          <t>60988; 68465</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60226; 68535</t>
+          <t>52665; 63360</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52544; 62967</t>
+          <t>122876; 132659</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>120291; 131524</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>123658; 132806</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>120461; 131841</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>104372; 119846</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>104077; 120236</t>
         </is>
       </c>
     </row>
@@ -2712,47 +2259,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>108</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
           <t>193</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2780,47 +2312,32 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>73884</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>73884</t>
+          <t>73026</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73026</t>
+          <t>71503</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71503</t>
+          <t>141319</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>141503</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>141319</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>141503</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
           <t>139268</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62243; 70379</t>
+          <t>62614; 70570</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62940; 72572</t>
+          <t>62937; 72343</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61445; 71756</t>
+          <t>62153; 71638</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>68614; 76608</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>70089; 76728</t>
+          <t>66237; 77140</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67166; 77239</t>
+          <t>64978; 75731</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66019; 76026</t>
+          <t>135498; 146014</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>133309; 147409</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>134372; 145537</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>133448; 147533</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>131966; 145915</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>132217; 145771</t>
         </is>
       </c>
     </row>
@@ -2920,47 +2422,32 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>111</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>108</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
           <t>116</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2988,47 +2475,32 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42013</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>42013</t>
+          <t>39582</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39582</t>
+          <t>38864</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38864</t>
+          <t>77229</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>79824</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>77229</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>79824</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
           <t>79700</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -3041,62 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31298; 37909</t>
+          <t>30515; 37887</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>36020; 42550</t>
+          <t>36305; 42547</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37439; 42704</t>
+          <t>37474; 42807</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38443; 43444</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38419; 43445</t>
+          <t>34981; 43210</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34306; 43016</t>
+          <t>33829; 42441</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33849; 42274</t>
+          <t>72426; 80612</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>74136; 84369</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>72406; 80707</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>73611; 84342</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>73238; 83947</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>74041; 83970</t>
         </is>
       </c>
     </row>
@@ -3128,47 +2585,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>158</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>147</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
           <t>134</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -3196,47 +2638,32 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54920</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>54920</t>
+          <t>53470</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53470</t>
+          <t>50667</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>50667</t>
+          <t>104194</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105980</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>104194</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>105980</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
           <t>96002</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -3249,62 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>44477; 52076</t>
+          <t>44558; 52090</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48110; 54766</t>
+          <t>48743; 54532</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39588; 49326</t>
+          <t>40445; 49145</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>50735; 57312</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>51204; 57313</t>
+          <t>48002; 56598</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48637; 56963</t>
+          <t>44964; 54296</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45756; 54351</t>
+          <t>98341; 108277</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>99722; 110223</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>98044; 108153</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>100360; 110436</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>88705; 101835</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>88433; 101383</t>
         </is>
       </c>
     </row>
@@ -3336,47 +2748,32 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>186</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>352</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>353</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
           <t>315</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -3404,47 +2801,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>124240</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>124240</t>
+          <t>130870</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>130870</t>
+          <t>113306</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>113306</t>
+          <t>242895</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>251537</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>242895</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>251537</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
           <t>212404</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -3457,62 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>113006; 122889</t>
+          <t>112974; 122950</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>112889; 126465</t>
+          <t>113175; 126510</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>89395; 106134</t>
+          <t>89833; 107566</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>119053; 128825</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>118402; 128907</t>
+          <t>123409; 136546</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>123625; 135826</t>
+          <t>104159; 120372</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>104611; 121155</t>
+          <t>235240; 249036</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>241722; 258983</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>235459; 249319</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>241978; 260020</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>200251; 223316</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>200949; 224067</t>
         </is>
       </c>
     </row>
@@ -3544,47 +2911,32 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>225</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>450</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>429</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
           <t>457</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -3612,47 +2964,32 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>151084</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>151084</t>
+          <t>147049</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>147049</t>
+          <t>150703</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>150703</t>
+          <t>293060</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>288896</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>293060</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>288896</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
           <t>296378</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>134949; 146777</t>
+          <t>135217; 146624</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>134138; 148089</t>
+          <t>134077; 148507</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>137730; 151784</t>
+          <t>139162; 152118</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>144697; 155535</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>145603; 155753</t>
+          <t>139347; 153278</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>138910; 153713</t>
+          <t>142918; 156487</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>143327; 156895</t>
+          <t>283106; 300008</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>276374; 298275</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>284679; 300218</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>278838; 299088</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>286793; 305328</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>287061; 305827</t>
         </is>
       </c>
     </row>
@@ -3752,47 +3074,32 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>993</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>947</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>893</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
           <t>1789</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -3820,47 +3127,32 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>661138</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>661138</t>
+          <t>665232</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>665232</t>
+          <t>622770</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>622770</t>
+          <t>1272611</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1298955</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1272611</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>1298955</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
           <t>1215045</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>598015; 623118</t>
+          <t>597408; 622663</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>619496; 646671</t>
+          <t>620351; 647122</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>573893; 606252</t>
+          <t>576591; 607939</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>648998; 671824</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>648912; 671860</t>
+          <t>649515; 678391</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>649341; 679132</t>
+          <t>604626; 638256</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>605264; 638164</t>
+          <t>1255897; 1287529</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1277477; 1317922</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1255626; 1288520</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>1279167; 1318438</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>1192798; 1236343</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>1192569; 1236573</t>
         </is>
       </c>
     </row>
@@ -3941,17 +3218,17 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
     <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_dic/IP41-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP41-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>85,69%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>90,98%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>84,95%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>87,84%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>93,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>87,35%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>85,69%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>90,98%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,47; 93,82</t>
+          <t>75,96; 91,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,3; 97,33</t>
+          <t>84,18; 96,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,11; 93,09</t>
+          <t>76,37; 91,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77,22; 91,87</t>
+          <t>79,31; 93,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,73; 95,34</t>
+          <t>85,87; 97,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,66; 91,09</t>
+          <t>78,85; 93,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,85; 91,3</t>
+          <t>79,97; 90,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87,3; 95,25</t>
+          <t>87,55; 95,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79,59; 90,46</t>
+          <t>79,52; 90,75</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>92,34%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>87,36%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>77,59%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>90,63%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>91,28%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>86,47%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>92,34%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>87,36%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>77,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,77; 94,72</t>
+          <t>87,25; 95,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,09; 95,04</t>
+          <t>81,33; 91,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80,57; 91,06</t>
+          <t>69,72; 83,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87,66; 95,99</t>
+          <t>85,1; 94,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>82,08; 92,01</t>
+          <t>85,47; 95,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,26; 84,57</t>
+          <t>80,34; 90,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,26; 94,39</t>
+          <t>87,61; 94,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>85,26; 92,19</t>
+          <t>85,22; 92,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>77,21; 85,79</t>
+          <t>76,77; 85,7</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>93,71%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>91,45%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>83,54%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>94,49%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>90,43%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>81,33%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>93,71%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>91,45%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88,29; 97,84</t>
+          <t>87,83; 97,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,6; 95,51</t>
+          <t>84,7; 95,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71,04; 88,52</t>
+          <t>75,5; 89,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87,41; 97,3</t>
+          <t>87,67; 97,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>85,59; 96,09</t>
+          <t>83,29; 95,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75,34; 90,64</t>
+          <t>71,41; 88,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,49; 96,61</t>
+          <t>90,41; 96,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>86,27; 94,33</t>
+          <t>86,43; 94,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>76,12; 87,93</t>
+          <t>75,96; 87,73</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>93,39%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>88,8%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>88,07%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>91,9%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>88,06%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>88,05%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>93,39%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>88,8%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>88,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85,33; 96,17</t>
+          <t>87,66; 96,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80,94; 93,03</t>
+          <t>81,17; 93,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,76; 93,08</t>
+          <t>81,42; 93,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86,73; 96,84</t>
+          <t>85,6; 96,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,55; 93,81</t>
+          <t>80,28; 93,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,04; 93,28</t>
+          <t>80,5; 93,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,86; 95,75</t>
+          <t>88,53; 95,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,32; 92,13</t>
+          <t>83,66; 92,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>83,61; 92,18</t>
+          <t>83,34; 92,03</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95,23%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>84,66%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>83,85%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>87,09%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>91,66%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>94,01%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>95,23%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>84,66%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>83,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>75,46; 93,69</t>
+          <t>87,32; 98,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,7; 96,92</t>
+          <t>74,9; 91,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,27; 98,55</t>
+          <t>72,69; 91,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87,14; 98,48</t>
+          <t>76,85; 93,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>74,82; 92,42</t>
+          <t>81,09; 96,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,99; 91,57</t>
+          <t>85,42; 98,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,66; 95,34</t>
+          <t>84,96; 95,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>81,78; 93,07</t>
+          <t>81,31; 92,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>82,46; 93,52</t>
+          <t>82,02; 93,27</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>92,9%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>88,75%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>87,75%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>87,9%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>93,79%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>83,53%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>92,9%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>88,75%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>79,49; 92,93</t>
+          <t>86,65; 97,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>87,06; 97,4</t>
+          <t>79,94; 93,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74,52; 90,55</t>
+          <t>78,25; 93,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85,82; 96,94</t>
+          <t>77,61; 93,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>79,68; 93,95</t>
+          <t>86,05; 97,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>77,87; 94,04</t>
+          <t>73,23; 90,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85,38; 94,01</t>
+          <t>85,29; 94,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>85,8; 94,83</t>
+          <t>85,78; 94,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78,95; 90,51</t>
+          <t>79,39; 90,87</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>92,52%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>89,8%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>78,65%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>92,75%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>86,99%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>72,14%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>92,52%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>78,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,31; 96,1</t>
+          <t>88,22; 95,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>81,59; 91,2</t>
+          <t>84,47; 93,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65,39; 78,3</t>
+          <t>72,81; 83,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>88,66; 95,93</t>
+          <t>88,79; 96,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,68; 93,69</t>
+          <t>81,76; 91,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,3; 83,55</t>
+          <t>65,8; 78,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,71; 94,97</t>
+          <t>89,24; 94,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>84,98; 91,04</t>
+          <t>85,02; 91,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>71,4; 79,61</t>
+          <t>70,83; 79,55</t>
         </is>
       </c>
     </row>
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>92,7%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>85,84%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>88,21%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>91,45%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>86,12%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>88,73%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>92,7%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>85,84%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>88,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>87,09; 94,44</t>
+          <t>88,5; 95,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>81,4; 90,16</t>
+          <t>80,91; 89,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84,76; 92,66</t>
+          <t>84,35; 92,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88,78; 95,43</t>
+          <t>87,7; 94,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>81,34; 89,47</t>
+          <t>80,9; 90,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,65; 91,59</t>
+          <t>83,98; 91,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,96; 94,27</t>
+          <t>89,15; 94,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>82,25; 88,77</t>
+          <t>82,91; 89,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>85,68; 91,28</t>
+          <t>85,46; 91,06</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>92,38%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>88,28%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>83,76%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>91,09%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>89,17%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>84,19%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>88,28%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>83,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>89,0; 92,76</t>
+          <t>90,57; 93,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87,29; 91,06</t>
+          <t>86,16; 90,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>81,96; 86,42</t>
+          <t>81,43; 85,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>90,69; 93,88</t>
+          <t>89,21; 92,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>86,2; 90,03</t>
+          <t>87,23; 91,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>81,32; 85,84</t>
+          <t>81,72; 86,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>90,55; 92,83</t>
+          <t>90,55; 92,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>87,25; 90,01</t>
+          <t>87,33; 89,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>82,42; 85,46</t>
+          <t>82,22; 85,45</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,32 +1755,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>81</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>50434</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>58962</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>54761</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>45577</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>52742</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>50113</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>50434</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>58962</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>54761</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40712; 48676</t>
+          <t>44708; 54080</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48373; 55193</t>
+          <t>54553; 62294</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45384; 53407</t>
+          <t>49228; 59083</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45450; 54075</t>
+          <t>41148; 48680</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>54265; 61787</t>
+          <t>48698; 55016</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48128; 58721</t>
+          <t>45239; 53528</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89534; 101105</t>
+          <t>88563; 100719</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>106088; 115743</t>
+          <t>106385; 115963</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>96970; 110208</t>
+          <t>96876; 110562</t>
         </is>
       </c>
     </row>
@@ -1918,32 +1918,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>139</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>134</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>99234</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>97112</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>84568</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>89471</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>95586</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>89101</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>99234</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97112</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84568</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83686; 93507</t>
+          <t>93758; 102951</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89095; 99519</t>
+          <t>90411; 102077</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83021; 93829</t>
+          <t>75997; 91198</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94205; 103156</t>
+          <t>84007; 93363</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91238; 102278</t>
+          <t>89494; 99584</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77667; 92174</t>
+          <t>82789; 93670</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>181966; 194621</t>
+          <t>180631; 194414</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>184050; 199009</t>
+          <t>183971; 198649</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>163712; 181906</t>
+          <t>162792; 181718</t>
         </is>
       </c>
     </row>
@@ -2081,32 +2081,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>74</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>65329</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>65161</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>58399</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>63870</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>61653</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>54353</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>65329</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>65161</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>58399</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>59684; 66134</t>
+          <t>61226; 67831</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56997; 65114</t>
+          <t>60356; 67889</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47477; 59160</t>
+          <t>52780; 62905</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60938; 67826</t>
+          <t>59263; 66128</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>60988; 68465</t>
+          <t>56788; 65108</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>52665; 63360</t>
+          <t>47723; 59444</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>122876; 132659</t>
+          <t>124138; 132631</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>120291; 131524</t>
+          <t>120505; 131517</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>104077; 120236</t>
+          <t>103860; 119957</t>
         </is>
       </c>
     </row>
@@ -2244,32 +2244,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>99</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>73884</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>73026</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>71503</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>67435</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>68477</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>67765</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>73884</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>73026</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>71503</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62614; 70570</t>
+          <t>69351; 76538</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62937; 72343</t>
+          <t>66751; 76900</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62153; 71638</t>
+          <t>66100; 75702</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>68614; 76608</t>
+          <t>62814; 70549</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>66237; 77140</t>
+          <t>62424; 72565</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>64978; 75731</t>
+          <t>61957; 72063</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>135498; 146014</t>
+          <t>134994; 146084</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>133309; 147409</t>
+          <t>133857; 147965</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>132217; 145771</t>
+          <t>131791; 145539</t>
         </is>
       </c>
     </row>
@@ -2407,32 +2407,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>59</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2460,32 +2460,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>42013</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>39582</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>38864</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>35216</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>40241</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>40836</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>42013</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>39582</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>38864</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30515; 37887</t>
+          <t>38522; 43443</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>36305; 42547</t>
+          <t>35019; 42925</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37474; 42807</t>
+          <t>33694; 42229</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38443; 43444</t>
+          <t>31078; 37926</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>34981; 43210</t>
+          <t>35598; 42556</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33829; 42441</t>
+          <t>37104; 42784</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>72426; 80612</t>
+          <t>71835; 80610</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>74136; 84369</t>
+          <t>73712; 84108</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>74041; 83970</t>
+          <t>73643; 83749</t>
         </is>
       </c>
     </row>
@@ -2570,27 +2570,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>74</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>54920</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>53470</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>50667</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>49274</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>52510</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>45335</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>54920</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>53470</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>50667</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>44558; 52090</t>
+          <t>51228; 57380</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48743; 54532</t>
+          <t>48160; 56494</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40445; 49145</t>
+          <t>45178; 53997</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50735; 57312</t>
+          <t>43502; 52610</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>48002; 56598</t>
+          <t>48176; 54763</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44964; 54296</t>
+          <t>39742; 49206</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>98341; 108277</t>
+          <t>98236; 108628</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>99722; 110223</t>
+          <t>99703; 110234</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>88433; 101383</t>
+          <t>88923; 101787</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>167</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>150</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>124240</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>130870</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>113306</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>118655</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>120667</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>99098</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>124240</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>130870</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>113306</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>112974; 122950</t>
+          <t>118465; 128350</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>113175; 126510</t>
+          <t>123099; 136024</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>89833; 107566</t>
+          <t>104901; 120831</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>119053; 128825</t>
+          <t>113587; 122966</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>123409; 136546</t>
+          <t>113412; 126340</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>104159; 120372</t>
+          <t>90393; 107205</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>235240; 249036</t>
+          <t>233993; 248992</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>241722; 258983</t>
+          <t>241835; 259531</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>200949; 224067</t>
+          <t>199334; 223884</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>232</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>151084</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>147049</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>150703</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>141976</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>141847</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>145674</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>151084</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>147049</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>150703</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>135217; 146624</t>
+          <t>144242; 155512</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>134077; 148507</t>
+          <t>138618; 153609</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>139162; 152118</t>
+          <t>144116; 157238</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>144697; 155535</t>
+          <t>136156; 147004</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>139347; 153278</t>
+          <t>133255; 148360</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>142918; 156487</t>
+          <t>137879; 150587</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>283106; 300008</t>
+          <t>283699; 299923</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>276374; 298275</t>
+          <t>278595; 299753</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>287061; 305827</t>
+          <t>286327; 305062</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>916</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>912</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>896</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>893</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>661138</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>665232</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>622770</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>611473</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>633723</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>592276</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>661138</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>665232</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>622770</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>597408; 622663</t>
+          <t>648186; 672164</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>620351; 647122</t>
+          <t>649247; 679152</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>576591; 607939</t>
+          <t>605446; 638865</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>648998; 671824</t>
+          <t>598853; 622097</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>649515; 678391</t>
+          <t>619897; 647022</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>604626; 638256</t>
+          <t>574859; 607310</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1255897; 1287529</t>
+          <t>1255890; 1289194</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1277477; 1317922</t>
+          <t>1278637; 1317666</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1192569; 1236573</t>
+          <t>1189699; 1236418</t>
         </is>
       </c>
     </row>
